--- a/data/trans_dic/P56$auxiliar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,72</t>
+          <t>0,0; 49,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,61</t>
+          <t>0,0; 61,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 56,17</t>
+          <t>15,05; 55,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,6</t>
+          <t>0,0; 28,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,63; 69,99</t>
+          <t>14,84; 68,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 42,18</t>
+          <t>11,22; 42,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 27,27</t>
+          <t>2,66; 27,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 54,65</t>
+          <t>13,03; 53,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 48,87</t>
+          <t>6,47; 48,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 35,6</t>
+          <t>8,47; 33,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,48</t>
+          <t>0,0; 36,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 33,45</t>
+          <t>13,82; 33,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 25,12</t>
+          <t>6,2; 26,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,05</t>
+          <t>0,0; 30,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 31,66</t>
+          <t>14,52; 32,95</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 51,85</t>
+          <t>17,67; 51,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 61,86</t>
+          <t>17,17; 66,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 42,22</t>
+          <t>19,92; 42,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 46,56</t>
+          <t>11,1; 45,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,65; 41,08</t>
+          <t>22,48; 41,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,99</t>
+          <t>0,0; 52,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 50,91</t>
+          <t>6,4; 49,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 70,35</t>
+          <t>9,77; 62,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 34,45</t>
+          <t>4,47; 34,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,18</t>
+          <t>0,0; 26,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 53,1</t>
+          <t>26,75; 54,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 49,91</t>
+          <t>7,86; 54,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 27,86</t>
+          <t>3,24; 28,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 24,49</t>
+          <t>2,45; 23,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,98; 47,94</t>
+          <t>23,38; 48,18</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,93; 66,39</t>
+          <t>19,77; 65,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 52,44</t>
+          <t>10,32; 48,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,6</t>
+          <t>0,0; 48,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,49; 52,26</t>
+          <t>22,44; 51,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,76; 54,87</t>
+          <t>16,28; 53,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,87</t>
+          <t>0,0; 52,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,58; 51,21</t>
+          <t>25,51; 51,24</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,07; 70,35</t>
+          <t>10,08; 70,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 27,31</t>
+          <t>4,76; 25,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 52,17</t>
+          <t>10,3; 52,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,29; 44,67</t>
+          <t>25,96; 45,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,79; 48,66</t>
+          <t>16,94; 48,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,74; 35,01</t>
+          <t>19,97; 34,9</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,23</t>
+          <t>0,0; 33,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 55,57</t>
+          <t>9,72; 56,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 29,78</t>
+          <t>5,63; 30,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 25,82</t>
+          <t>2,79; 24,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,32; 39,95</t>
+          <t>18,18; 39,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 25,02</t>
+          <t>4,32; 23,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 17,73</t>
+          <t>1,92; 18,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,14; 37,28</t>
+          <t>18,72; 37,86</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,1</t>
+          <t>0,0; 39,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 25,64</t>
+          <t>2,89; 25,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,32</t>
+          <t>3,12; 26,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,51</t>
+          <t>0,0; 16,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>0,0; 30,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,13</t>
+          <t>10,09; 25,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 16,85</t>
+          <t>1,86; 18,51</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 17,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,07</t>
+          <t>0,0; 25,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 22,24</t>
+          <t>10,11; 22,52</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,28; 20,49</t>
+          <t>5,47; 20,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,61</t>
+          <t>2,24; 13,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,82; 28,69</t>
+          <t>15,63; 29,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,79</t>
+          <t>2,34; 13,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,74; 26,28</t>
+          <t>14,2; 26,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,62</t>
+          <t>3,08; 11,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,52</t>
+          <t>23,68; 31,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,64; 10,23</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,32; 22,17</t>
+          <t>13,26; 21,85</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,07</t>
+          <t>3,68; 10,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,5; 29,15</t>
+          <t>22,57; 29,6</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1276</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1639</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 4948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3250</t>
+          <t>0; 3095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3130; 11928</t>
+          <t>3196; 11774</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6179</t>
+          <t>0; 5242</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1203; 5758</t>
+          <t>1221; 5670</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1564</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3189; 11933</t>
+          <t>3174; 11993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754; 7725</t>
+          <t>753; 7883</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1719; 7245</t>
+          <t>1727; 7135</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1599</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1449</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>812; 5963</t>
+          <t>789; 5886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3241; 13141</t>
+          <t>3128; 12489</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5609</t>
+          <t>0; 6525</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5986; 14022</t>
+          <t>5792; 13977</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1865</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2733; 12211</t>
+          <t>3015; 12916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5370</t>
+          <t>0; 7122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7993; 17136</t>
+          <t>7856; 17830</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1397</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3244; 9495</t>
+          <t>3236; 9486</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3321; 11911</t>
+          <t>3307; 12842</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2236</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6603; 14147</t>
+          <t>6677; 14281</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1797</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3368; 13279</t>
+          <t>3167; 13016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11738; 21289</t>
+          <t>11650; 21380</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1802</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 5214</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>603; 4723</t>
+          <t>593; 4625</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1055; 7608</t>
+          <t>1056; 6788</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1011; 7736</t>
+          <t>1004; 7856</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6026</t>
+          <t>0; 6598</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5332; 10500</t>
+          <t>5289; 10871</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1057; 6685</t>
+          <t>1053; 7252</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1018; 8674</t>
+          <t>1007; 8753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>832; 8554</t>
+          <t>857; 8160</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6967; 13927</t>
+          <t>6792; 13994</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1309</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1420; 4980</t>
+          <t>1483; 4919</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2045; 10330</t>
+          <t>2032; 9587</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5887</t>
+          <t>0; 5893</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3895; 8667</t>
+          <t>3721; 8565</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1783</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4425; 14487</t>
+          <t>4299; 14060</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6569</t>
+          <t>0; 6719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6160; 12335</t>
+          <t>6145; 12341</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1336</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1073; 7492</t>
+          <t>1073; 7494</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1458</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>792; 4513</t>
+          <t>787; 4159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2071; 10536</t>
+          <t>2080; 10536</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2329</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8031; 14187</t>
+          <t>8244; 14607</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5178; 15009</t>
+          <t>5226; 14913</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9530; 16904</t>
+          <t>9641; 16851</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1370</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5478</t>
+          <t>0; 5148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>864; 6895</t>
+          <t>1206; 7064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1864; 10551</t>
+          <t>1993; 10958</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1219; 11079</t>
+          <t>1196; 10560</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7262; 16751</t>
+          <t>7622; 16621</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1561</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2941; 12756</t>
+          <t>2203; 12226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1218; 11145</t>
+          <t>1205; 11338</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10399; 20255</t>
+          <t>10170; 20570</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1660</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 3629</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>604; 5334</t>
+          <t>602; 5397</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 8476</t>
+          <t>934; 7814</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5866</t>
+          <t>0; 5089</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 6781</t>
+          <t>0; 6957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5590; 14406</t>
+          <t>5785; 14773</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>923; 8282</t>
+          <t>915; 9096</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 5520</t>
+          <t>0; 6937</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 6713</t>
+          <t>0; 7972</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7814; 17374</t>
+          <t>7899; 17597</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4144; 16088</t>
+          <t>4292; 16169</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1641; 9814</t>
+          <t>1616; 9403</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16150; 29283</t>
+          <t>15949; 29888</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2942; 12902</t>
+          <t>2188; 12254</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30252; 53940</t>
+          <t>29141; 53902</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6053; 21681</t>
+          <t>5291; 20263</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>59722; 79133</t>
+          <t>59452; 79282</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2256; 12751</t>
+          <t>2331; 14510</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37799; 62918</t>
+          <t>37622; 61995</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8909; 24568</t>
+          <t>8984; 25963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>79430; 102926</t>
+          <t>79688; 104508</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$auxiliar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,82</t>
+          <t>0,0; 41,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,53</t>
+          <t>0,0; 56,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 55,44</t>
+          <t>10,42; 55,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,5</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 68,93</t>
+          <t>15,35; 65,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 42,4</t>
+          <t>7,91; 42,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 27,83</t>
+          <t>2,74; 25,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 53,82</t>
+          <t>13,3; 51,4</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 48,25</t>
+          <t>6,81; 49,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,47; 33,84</t>
+          <t>6,06; 32,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,62</t>
+          <t>0,0; 39,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 33,34</t>
+          <t>14,59; 34,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 26,57</t>
+          <t>4,7; 26,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,56</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,52; 32,95</t>
+          <t>14,56; 31,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,67; 51,8</t>
+          <t>16,17; 49,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 66,69</t>
+          <t>17,25; 66,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 42,62</t>
+          <t>19,76; 41,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,1; 45,63</t>
+          <t>11,52; 47,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 41,25</t>
+          <t>21,56; 40,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,11</t>
+          <t>0,0; 54,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 49,86</t>
+          <t>7,23; 52,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 62,77</t>
+          <t>9,78; 69,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 34,99</t>
+          <t>4,51; 37,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,47</t>
+          <t>0,0; 21,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,75; 54,98</t>
+          <t>25,94; 53,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 54,14</t>
+          <t>7,91; 55,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 28,11</t>
+          <t>3,24; 27,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 23,36</t>
+          <t>2,37; 22,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 48,18</t>
+          <t>24,75; 47,55</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,69; 84,7</t>
+          <t>3,32; 84,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 65,57</t>
+          <t>19,35; 66,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 48,67</t>
+          <t>10,11; 48,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,64</t>
+          <t>0,0; 47,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,44; 51,64</t>
+          <t>23,67; 51,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,28; 53,25</t>
+          <t>16,37; 53,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,03</t>
+          <t>0,0; 51,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,51; 51,24</t>
+          <t>24,87; 50,52</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,08; 70,36</t>
+          <t>10,1; 70,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 25,17</t>
+          <t>4,79; 26,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,3; 52,17</t>
+          <t>10,16; 47,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 45,99</t>
+          <t>25,08; 44,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 48,35</t>
+          <t>17,1; 48,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,97; 34,9</t>
+          <t>19,95; 36,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 56,93</t>
+          <t>9,12; 55,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 30,93</t>
+          <t>5,58; 31,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 24,61</t>
+          <t>2,81; 25,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,18; 39,64</t>
+          <t>17,44; 39,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,17 +1602,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 23,98</t>
+          <t>5,46; 24,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 18,04</t>
+          <t>1,9; 17,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 37,86</t>
+          <t>18,78; 37,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,87</t>
+          <t>0,0; 40,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,89; 25,95</t>
+          <t>2,85; 24,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 26,11</t>
+          <t>3,04; 25,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,93</t>
+          <t>0,0; 16,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,57</t>
+          <t>0,0; 29,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,09; 25,77</t>
+          <t>10,58; 27,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 18,51</t>
+          <t>1,89; 18,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,81</t>
+          <t>0,0; 14,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,02</t>
+          <t>0,0; 23,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,11; 22,52</t>
+          <t>10,62; 22,92</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1842,57 +1842,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,6</t>
+          <t>4,85; 20,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,04</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,63; 29,28</t>
+          <t>15,47; 28,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,1</t>
+          <t>2,41; 13,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,2; 26,26</t>
+          <t>14,51; 25,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,8</t>
+          <t>3,06; 12,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,68; 31,58</t>
+          <t>24,08; 31,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,23</t>
+          <t>1,62; 9,73</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,85</t>
+          <t>13,3; 23,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,65</t>
+          <t>3,67; 10,29</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>22,57; 29,6</t>
+          <t>22,61; 29,23</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3918</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4948</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3095</t>
+          <t>0; 2996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3196; 11774</t>
+          <t>2212; 11826</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>0; 6192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1221; 5670</t>
+          <t>1298; 5579</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3174; 11993</t>
+          <t>2238; 11921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753; 7883</t>
+          <t>775; 7088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1727; 7135</t>
+          <t>1825; 7053</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>13204</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>789; 5886</t>
+          <t>891; 6415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3128; 12489</t>
+          <t>2236; 12020</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6525</t>
+          <t>0; 6957</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5792; 13977</t>
+          <t>6523; 15413</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3015; 12916</t>
+          <t>2285; 12746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7122</t>
+          <t>0; 6725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7856; 17830</t>
+          <t>8412; 18340</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15776</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3236; 9486</t>
+          <t>2890; 8771</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3307; 12842</t>
+          <t>3321; 12867</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6677; 14281</t>
+          <t>6629; 13993</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3167; 13016</t>
+          <t>3285; 13504</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11650; 21380</t>
+          <t>11084; 20809</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10498</t>
         </is>
       </c>
     </row>
@@ -2843,52 +2843,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5214</t>
+          <t>0; 5405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>593; 4625</t>
+          <t>688; 5042</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1056; 6788</t>
+          <t>1057; 7497</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1004; 7856</t>
+          <t>1012; 8513</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6598</t>
+          <t>0; 5238</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5289; 10871</t>
+          <t>5401; 11192</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1053; 7252</t>
+          <t>1059; 7415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1007; 8753</t>
+          <t>1008; 8486</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>857; 8160</t>
+          <t>827; 7905</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6792; 13994</t>
+          <t>7510; 14428</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9462</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1119; 5680</t>
+          <t>222; 5673</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1483; 4919</t>
+          <t>1486; 5073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2032; 9587</t>
+          <t>1992; 9476</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5707</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3721; 8565</t>
+          <t>4076; 8853</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4299; 14060</t>
+          <t>4321; 14164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6719</t>
+          <t>0; 6686</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6145; 12341</t>
+          <t>6191; 12576</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>13177</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1073; 7494</t>
+          <t>1076; 7503</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>787; 4159</t>
+          <t>793; 4344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2080; 10536</t>
+          <t>2052; 9586</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8244; 14607</t>
+          <t>8162; 14469</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5226; 14913</t>
+          <t>5276; 14994</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9641; 16851</t>
+          <t>9795; 17722</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>18346</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5148</t>
+          <t>0; 5229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1206; 7064</t>
+          <t>1359; 8267</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1993; 10958</t>
+          <t>1978; 11092</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1196; 10560</t>
+          <t>1207; 10923</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7622; 16621</t>
+          <t>9007; 20240</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2203; 12226</t>
+          <t>2782; 12367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1205; 11338</t>
+          <t>1195; 10714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10170; 20570</t>
+          <t>12494; 25152</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>14394</t>
         </is>
       </c>
     </row>
@@ -3675,52 +3675,52 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3629</t>
+          <t>0; 3679</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>602; 5397</t>
+          <t>674; 5739</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>934; 7814</t>
+          <t>910; 7734</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5089</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 6957</t>
+          <t>0; 6767</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5785; 14773</t>
+          <t>7033; 18120</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>915; 9096</t>
+          <t>930; 9001</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 6937</t>
+          <t>0; 5469</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 7972</t>
+          <t>0; 7348</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7899; 17597</t>
+          <t>9583; 20674</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
     </row>
@@ -3878,57 +3878,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4292; 16169</t>
+          <t>3809; 15906</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1616; 9403</t>
+          <t>1575; 9401</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15949; 29888</t>
+          <t>16799; 31442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2188; 12254</t>
+          <t>2251; 12977</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29141; 53902</t>
+          <t>29788; 52982</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5291; 20263</t>
+          <t>5260; 20992</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>59452; 79282</t>
+          <t>66317; 86929</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2331; 14510</t>
+          <t>2297; 13806</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37622; 61995</t>
+          <t>37746; 65453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8984; 25963</t>
+          <t>8941; 25086</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>79688; 104508</t>
+          <t>86824; 112260</t>
         </is>
       </c>
     </row>
